--- a/SourceData/Datas/item.xlsx
+++ b/SourceData/Datas/item.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1056,7 +1056,52 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>display_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>use_condition_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>use_effect_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>max_stack</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>gm_grant</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>gm_amount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>sort</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1125,52 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>ItemType</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -1100,6 +1190,51 @@
           <t>c</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1114,68 +1249,268 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>物品类型</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>显示名</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>展示配置ID(→TDisplay.link_id)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>使用条件ID(0无)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>使用效果ID(0无)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>最大堆叠</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>GM可发放</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>GM单次数量</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>排序</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>grass</t>
+          <t>hand</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>草料</t>
-        </is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>手</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>拔除杂草与灌木，收获成熟作物</t>
+        </is>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>wood</t>
+          <t>hoe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>木料</t>
-        </is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>锄头</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1002</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>开垦荒地，翻出可种植的田地；也可挖起石头</t>
+        </is>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>dirt</t>
+          <t>can</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>泥土</t>
-        </is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>水壶</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1003</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>给作物浇水，促进生长</t>
+        </is>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>stone</t>
+          <t>axe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>石料</t>
-        </is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>斧头</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1004</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>砍伐野外的松树和橡树</t>
+        </is>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>fish</t>
+          <t>rod</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>鱼</t>
-        </is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>鱼竿</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1005</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>在湖边或码头抛竿钓鱼</t>
+        </is>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1186,116 +1521,555 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Seed</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>种子</t>
         </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1006</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>999</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>在翻好的田地上播种</t>
+        </is>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>parsnip</t>
+          <t>boost</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>防风草</t>
-        </is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>催熟剂</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1007</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>999</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>点在生长中的作物上，立刻催熟</t>
+        </is>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>boost</t>
+          <t>parsnip</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>催熟剂</t>
-        </is>
+          <t>Crop</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>防风草</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1008</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>999</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>刚收获的作物，可以出售或食用</t>
+        </is>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>copper</t>
+          <t>grass</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>铜矿石</t>
-        </is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>草料</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1009</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>999</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>拔除杂草与灌木获得</t>
+        </is>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>wood</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>铁矿石</t>
-        </is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>木料</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>999</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>砍伐树木获得，可用于建造</t>
+        </is>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>goldOre</t>
+          <t>dirt</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>金矿石</t>
-        </is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>泥土</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1011</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>999</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>锄地开垦时翻出的土壤</t>
+        </is>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" t="n">
+        <v>110</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>can</t>
+          <t>stone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>水壶</t>
-        </is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>石料</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1012</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>999</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>用锄头挖开石子与岩石获得</t>
+        </is>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>axe</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>斧头</t>
-        </is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>鱼</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1013</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>999</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>从湖里钓上来的鲜鱼</t>
+        </is>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>rod</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>鱼竿</t>
-        </is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>铜矿石</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1014</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>999</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>浅层矿洞可采，也可在矿脉商会购买</t>
+        </is>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>hoe</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>锄头</t>
-        </is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>铁矿石</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1015</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>999</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>矿洞深处的硬脉，锻造常用</t>
+        </is>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>goldOre</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>金矿石</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1016</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>999</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>稀有闪光矿脉</t>
+        </is>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>金币</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1017</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>999999</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>溪谷通用货币，可在商店买卖</t>
+        </is>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>500</v>
+      </c>
+      <c r="L22" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>recipeScroll</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Recipe</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>配方卷轴</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1018</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>点按打开，学习后解锁工作台配方</t>
+        </is>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
